--- a/public/PICO_3_Finances.xlsx
+++ b/public/PICO_3_Finances.xlsx
@@ -546,7 +546,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Digital = Email (PICO_EM_* ref codes) + SMS (PICO_SMS_* ref codes). Yellow = manual input.</t>
+          <t>Digital = Email (PICO_EM_* ref codes) + SMS (SMS_* ref codes). Yellow = manual input.</t>
         </is>
       </c>
     </row>
